--- a/Generators/Experiment with utility data leak/utility results/4. Forest cover dataset/TRTR_TSTR_results_merged.xlsx
+++ b/Generators/Experiment with utility data leak/utility results/4. Forest cover dataset/TRTR_TSTR_results_merged.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CTGAN" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CopulaGAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TVAE" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="GaussianCopula" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="WGAN_GP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CTABGAN" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTGAN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopulaGAN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVAE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaussianCopula" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WGAN_GP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTABGAN" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,13 +27,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +47,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +55,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,67 +439,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)</t>
         </is>
@@ -998,6 +1012,2578 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>0.4790 ± 0.0490</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy Std_TRTR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>F1 Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>F1 Std_TRTR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Precision Std_TRTR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Recall Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Recall Std_TRTR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>F1 (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Precision (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Recall (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy Std_TSTR</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>F1 Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>F1 Std_TSTR</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Precision Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Precision Std_TSTR</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Recall Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Recall Std_TSTR</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>F1 (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Precision (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Recall (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy_Drop</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>F1_Drop</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Precision_Drop</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Recall_Drop</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6915000000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01795828499606793</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6842708000954391</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.01859935929962071</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6880344473978813</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.02207988225904673</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6915000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.01795828499606793</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.6915 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.6843 ± 0.0186</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.6880 ± 0.0221</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.6915 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02043961295567453</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3679534241036536</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.01699372937395863</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.3445775327134274</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.01574036430368459</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.02043961295567453</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.3970 ± 0.0204</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.3680 ± 0.0170</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.3446 ± 0.0157</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.3970 ± 0.0204</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.2945000000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.3163173759917855</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3434569146844539</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.2945000000000001</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6824999999999999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.01889297341459103</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6620033516331233</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.02172625840012613</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6586544948108609</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03419179007442599</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6824999999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.01889297341459103</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6825 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6620 ± 0.0217</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6587 ± 0.0342</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6825 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0196920739836559</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3668947705602713</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.02080501275150294</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.3387221489716747</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.02024400888026048</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.0196920739836559</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.4040 ± 0.0197</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.3669 ± 0.0208</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.3387 ± 0.0202</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.4040 ± 0.0197</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2784999999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.295108581072852</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.3199323458391862</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.2784999999999999</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.01901023116347847</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6603024352232341</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.02103640141418547</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6582702794717087</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03322025422810114</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01901023116347847</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.6815 ± 0.0190</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.6603 ± 0.0210</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.6583 ± 0.0332</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.6815 ± 0.0190</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03825717071492756</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3598347046068729</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.03555413680180423</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3324620631174764</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.03334365948789342</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.03825717071492756</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.3945 ± 0.0383</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.3598 ± 0.0356</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.3325 ± 0.0333</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.3945 ± 0.0383</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.3004677306163611</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3258082163542322</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LogReg</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6565000000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.01375378735718518</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6313197104590105</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.01421577326312037</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6373054542536021</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02103357911065157</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6565000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01375378735718518</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.6565 ± 0.0138</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.6313 ± 0.0142</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.6373 ± 0.0210</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.6565 ± 0.0138</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01461544084559584</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.3577613950957352</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01663777755632596</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3449775088276731</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01750160275012201</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.01461544084559584</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.4495 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.3578 ± 0.0166</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.3450 ± 0.0175</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.4495 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.2070000000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.2735583153632752</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.2923279454259289</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.2070000000000001</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AdaBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6485000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0277938842193746</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6197203841913493</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.02257514059906696</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6169118549430458</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02585545016933022</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6485000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0277938842193746</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.6485 ± 0.0278</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.6197 ± 0.0226</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.6169 ± 0.0259</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.6485 ± 0.0278</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03786305733972246</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.3965213261129702</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.03866573529246271</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3775309020878906</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.03355990332230687</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.03786305733972246</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.4565 ± 0.0379</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.3965 ± 0.0387</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.3775 ± 0.0336</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.4565 ± 0.0379</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1920000000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.2231990580783791</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.2393809528551551</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1920000000000001</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SVM-RBF</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01559914527573013</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6088274369756455</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01724800626160898</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5934847271911072</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01694453727725683</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.01559914527573013</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.6410 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.6088 ± 0.0172</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.5935 ± 0.0169</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.6410 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01358103252497557</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.3566820137587634</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.01683616476888826</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3471200818130427</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01916036594151319</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.01358103252497557</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.4520 ± 0.0136</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.3567 ± 0.0168</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.3471 ± 0.0192</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.4520 ± 0.0136</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1890000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.252145423216882</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.2463646453780645</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1890000000000001</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.02309401076758502</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6033478482984258</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.02356654708418312</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.606079712711094</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02256827610673722</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.02309401076758502</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.6100 ± 0.0231</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.6033 ± 0.0236</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.6061 ± 0.0226</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.6100 ± 0.0231</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03169297153067923</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.3582216295942252</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.02919024156897964</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3581887156779363</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.02728331858398704</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.03169297153067923</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.3610 ± 0.0317</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.3582 ± 0.0292</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.3582 ± 0.0273</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.3610 ± 0.0317</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.2489999999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.2451262187042006</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.2478909970331576</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.2489999999999999</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01986062547968833</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5858781958136642</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02033358207599369</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5834680764277166</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0316096947074111</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01986062547968833</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.6050 ± 0.0199</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.5859 ± 0.0203</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.5835 ± 0.0316</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.6050 ± 0.0199</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.02656229575084872</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.3748652676838536</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.02276822334220865</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.353983128703715</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.02023908185962098</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.02656229575084872</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.4000 ± 0.0266</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.3749 ± 0.0228</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.3540 ± 0.0202</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.4000 ± 0.0266</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.2110129281298106</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.2294849477240016</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01873795909674028</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5954974166913147</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01537663987626775</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.597796051914373</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01254810544324626</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01873795909674028</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.5980 ± 0.0187</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.5955 ± 0.0154</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.5978 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.5980 ± 0.0187</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4595000000000001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.02842631800911885</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.3577766801027361</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.02948681369571991</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3435025283610131</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.04901469741189243</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4595000000000001</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.02842631800911885</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.4595 ± 0.0284</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.3578 ± 0.0295</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.3435 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.4595 ± 0.0284</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.1384999999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.2377207365885786</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.2542935235533599</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.1384999999999999</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0490351347958221</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4505811915597158</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.04196827183233348</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5037432322871089</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.04596200128273002</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0490351347958221</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.4790 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.4506 ± 0.0420</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.5037 ± 0.0460</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.4790 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07432847517756719</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3178181169887249</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.05878019035439856</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.340422379798199</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.04889451401632575</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.07432847517756719</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.3395 ± 0.0743</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.3178 ± 0.0588</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.3404 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.3395 ± 0.0743</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1327630745709908</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1633208524889099</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy Std_TRTR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>F1 Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>F1 Std_TRTR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Precision Std_TRTR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Recall Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Recall Std_TRTR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>F1 (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Precision (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Recall (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy Std_TSTR</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>F1 Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>F1 Std_TSTR</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Precision Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Precision Std_TSTR</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Recall Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Recall Std_TSTR</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>F1 (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Precision (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Recall (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy_Drop</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>F1_Drop</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Precision_Drop</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Recall_Drop</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6915000000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01795828499606793</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6842708000954391</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.01859935929962071</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6880344473978813</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.02207988225904673</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6915000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.01795828499606793</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.6915 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.6843 ± 0.0186</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.6880 ± 0.0221</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.6915 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7370000000000001</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01602081978759724</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.7319112840234987</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0147261780890411</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.7367811162280324</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.01443071785059797</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.7370000000000001</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.01602081978759724</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.7370 ± 0.0160</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.7319 ± 0.0147</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.7368 ± 0.0144</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.7370 ± 0.0160</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.04549999999999998</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.04764048392805964</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.04874666883015111</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.04549999999999998</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6824999999999999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.01889297341459103</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6620033516331233</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.02172625840012613</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6586544948108609</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03419179007442599</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6824999999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.01889297341459103</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6825 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6620 ± 0.0217</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6587 ± 0.0342</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6825 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01885618083164126</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.7925613107333307</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.01921193084959216</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8060859554191726</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.01852151631698142</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.01885618083164126</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.8000 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.7926 ± 0.0192</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.8061 ± 0.0185</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.8000 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.1175000000000002</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.1305579591002074</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.1474314606083117</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.1175000000000002</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.01901023116347847</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6603024352232341</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.02103640141418547</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6582702794717087</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03322025422810114</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01901023116347847</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.6815 ± 0.0190</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.6603 ± 0.0210</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.6583 ± 0.0332</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.6815 ± 0.0190</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01229272594305719</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7706256644923173</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01365942583992562</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.7798718047191795</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01517891656354376</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01229272594305719</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.7780 ± 0.0123</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.7706 ± 0.0137</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.7799 ± 0.0152</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.7780 ± 0.0123</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.09650000000000003</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.1103232292690832</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.1216015252474708</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.09650000000000003</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LogReg</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6565000000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.01375378735718518</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6313197104590105</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.01421577326312037</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6373054542536021</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02103357911065157</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6565000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01375378735718518</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.6565 ± 0.0138</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.6313 ± 0.0142</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.6373 ± 0.0210</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.6565 ± 0.0138</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01437590576856523</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.6422214226020916</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01502200332654791</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.6596251684653254</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01450248257564228</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.01437590576856523</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.6670 ± 0.0144</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.6422 ± 0.0150</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.6596 ± 0.0145</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.6670 ± 0.0144</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.01049999999999995</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.01090171214308111</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.0223197142117233</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.01049999999999995</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AdaBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6485000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0277938842193746</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6197203841913493</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.02257514059906696</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6169118549430458</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02585545016933022</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6485000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0277938842193746</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.6485 ± 0.0278</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.6197 ± 0.0226</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.6169 ± 0.0259</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.6485 ± 0.0278</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01179689224612422</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.6518767335774948</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01457311549350935</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.6328945341611686</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.01251393290058155</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.01179689224612422</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.6835 ± 0.0118</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.6519 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.6329 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.6835 ± 0.0118</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.03499999999999992</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.03215634938614542</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.0159826792181228</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.03499999999999992</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SVM-RBF</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01559914527573013</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6088274369756455</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01724800626160898</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5934847271911072</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01694453727725683</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.01559914527573013</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.6410 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.6088 ± 0.0172</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.5935 ± 0.0169</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.6410 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01189070598782466</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.6244192109293536</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.01121575106268233</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.6171991558255285</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01002019682678503</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.01189070598782466</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.6545 ± 0.0119</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.6244 ± 0.0112</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.6172 ± 0.0100</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.6545 ± 0.0119</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.01349999999999996</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.01559177395370814</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.0237144286344213</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.01349999999999996</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.02309401076758502</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6033478482984258</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.02356654708418312</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.606079712711094</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02256827610673722</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.02309401076758502</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.6100 ± 0.0231</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.6033 ± 0.0236</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.6061 ± 0.0226</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.6100 ± 0.0231</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6940000000000001</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03071373199943849</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.6934335297060754</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.03087203593058311</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.7001694360737535</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.03054887915144803</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.6940000000000001</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.03071373199943849</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.6940 ± 0.0307</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.6934 ± 0.0309</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.7002 ± 0.0305</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.6940 ± 0.0307</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.08400000000000007</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.09008568140764961</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.09408972336265953</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.08400000000000007</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01986062547968833</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5858781958136642</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02033358207599369</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5834680764277166</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0316096947074111</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01986062547968833</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.6050 ± 0.0199</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.5859 ± 0.0203</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.5835 ± 0.0316</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.6050 ± 0.0199</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6705</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01461544084559582</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.657702073134006</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01494329367897678</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6678716409567713</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01765617370511195</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6705</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.01461544084559582</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.6705 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.6577 ± 0.0149</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.6679 ± 0.0177</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.6705 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.0655</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.07182387732034179</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.08440356452905473</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.0655</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01873795909674028</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5954974166913147</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01537663987626775</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.597796051914373</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01254810544324626</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01873795909674028</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.5980 ± 0.0187</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.5955 ± 0.0154</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.5978 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.5980 ± 0.0187</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01131616346451198</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.6407364849544483</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.0125368861053302</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.6368794588622861</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.01452284264908751</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01131616346451198</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.6465 ± 0.0113</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.6407 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.6369 ± 0.0145</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.6465 ± 0.0113</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.04849999999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.04523906826313362</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.03908340694791312</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.04849999999999999</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0490351347958221</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4505811915597158</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.04196827183233348</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5037432322871089</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.04596200128273002</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0490351347958221</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.4790 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.4506 ± 0.0420</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.5037 ± 0.0460</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.4790 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.04709328803319829</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.5131743292796098</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.03988950108068751</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5566850502909479</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.03148047504906855</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.04709328803319829</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.5170 ± 0.0471</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.5132 ± 0.0399</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.5567 ± 0.0315</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.5170 ± 0.0471</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.03800000000000003</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.06259313771989405</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.05294181800383901</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.03800000000000003</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -1012,156 +3598,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -7884,6 +10470,2246 @@
       <c r="AD61" t="inlineStr">
         <is>
           <t>CTABGAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.6915000000000001</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.01795828499606793</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.6842708000954391</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.01859935929962071</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.6880344473978813</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.02207988225904673</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.6915000000000001</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.01795828499606793</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.6915 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0.6843 ± 0.0186</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0.6880 ± 0.0221</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>0.6915 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0.7370000000000001</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.01602081978759724</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.7319112840234987</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.0147261780890411</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.7367811162280324</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.01443071785059797</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.7370000000000001</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0.01602081978759724</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0.7370 ± 0.0160</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>0.7319 ± 0.0147</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>0.7368 ± 0.0144</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>0.7370 ± 0.0160</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>-0.04549999999999998</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-0.04764048392805964</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>-0.04874666883015111</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>-0.04549999999999998</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.6824999999999999</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.01889297341459103</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.6620033516331233</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.02172625840012613</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.6586544948108609</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.03419179007442599</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.6824999999999999</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.01889297341459103</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.6825 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0.6620 ± 0.0217</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0.6587 ± 0.0342</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>0.6825 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.01885618083164126</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.7925613107333307</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.01921193084959216</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.8060859554191726</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.01852151631698142</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0.01885618083164126</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0.8000 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>0.7926 ± 0.0192</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>0.8061 ± 0.0185</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>0.8000 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>-0.1175000000000002</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-0.1305579591002074</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>-0.1474314606083117</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>-0.1175000000000002</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.01901023116347847</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.6603024352232341</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.02103640141418547</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.6582702794717087</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.03322025422810114</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.01901023116347847</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.6815 ± 0.0190</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0.6603 ± 0.0210</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0.6583 ± 0.0332</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>0.6815 ± 0.0190</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.01229272594305719</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.7706256644923173</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.01365942583992562</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.7798718047191795</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.01517891656354376</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0.01229272594305719</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0.7780 ± 0.0123</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>0.7706 ± 0.0137</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>0.7799 ± 0.0152</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>0.7780 ± 0.0123</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.09650000000000003</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-0.1103232292690832</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-0.1216015252474708</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>-0.09650000000000003</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LogReg</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.6565000000000001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.01375378735718518</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.6313197104590105</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.01421577326312037</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.6373054542536021</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.02103357911065157</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.6565000000000001</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.01375378735718518</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.6565 ± 0.0138</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0.6313 ± 0.0142</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0.6373 ± 0.0210</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>0.6565 ± 0.0138</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.01437590576856523</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.6422214226020916</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.01502200332654791</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.6596251684653254</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.01450248257564228</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0.01437590576856523</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0.6670 ± 0.0144</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>0.6422 ± 0.0150</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>0.6596 ± 0.0145</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>0.6670 ± 0.0144</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>-0.01049999999999995</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>-0.01090171214308111</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-0.0223197142117233</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>-0.01049999999999995</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AdaBoost</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.6485000000000001</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.0277938842193746</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.6197203841913493</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.02257514059906696</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.6169118549430458</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.02585545016933022</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.6485000000000001</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.0277938842193746</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.6485 ± 0.0278</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0.6197 ± 0.0226</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0.6169 ± 0.0259</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>0.6485 ± 0.0278</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.01179689224612422</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.6518767335774948</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.01457311549350935</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.6328945341611686</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.01251393290058155</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0.01179689224612422</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0.6835 ± 0.0118</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>0.6519 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>0.6329 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>0.6835 ± 0.0118</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>-0.03499999999999992</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>-0.03215634938614542</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>-0.0159826792181228</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>-0.03499999999999992</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SVM-RBF</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.01559914527573013</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.6088274369756455</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.01724800626160898</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.5934847271911072</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.01694453727725683</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.01559914527573013</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.6410 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0.6088 ± 0.0172</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0.5935 ± 0.0169</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>0.6410 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.01189070598782466</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.6244192109293536</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.01121575106268233</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.6171991558255285</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.01002019682678503</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.01189070598782466</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0.6545 ± 0.0119</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>0.6244 ± 0.0112</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>0.6172 ± 0.0100</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>0.6545 ± 0.0119</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>-0.01349999999999996</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>-0.01559177395370814</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-0.0237144286344213</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>-0.01349999999999996</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.02309401076758502</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.6033478482984258</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.02356654708418312</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.606079712711094</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.02256827610673722</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.02309401076758502</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.6100 ± 0.0231</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0.6033 ± 0.0236</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0.6061 ± 0.0226</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>0.6100 ± 0.0231</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0.6940000000000001</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.03071373199943849</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.6934335297060754</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.03087203593058311</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.7001694360737535</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.03054887915144803</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.6940000000000001</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0.03071373199943849</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0.6940 ± 0.0307</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>0.6934 ± 0.0309</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>0.7002 ± 0.0305</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>0.6940 ± 0.0307</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>-0.08400000000000007</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>-0.09008568140764961</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>-0.09408972336265953</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>-0.08400000000000007</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.01986062547968833</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.5858781958136642</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.02033358207599369</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.5834680764277166</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.0316096947074111</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.01986062547968833</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.6050 ± 0.0199</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0.5859 ± 0.0203</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0.5835 ± 0.0316</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>0.6050 ± 0.0199</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0.6705</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.01461544084559582</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.657702073134006</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.01494329367897678</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.6678716409567713</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.01765617370511195</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.6705</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.01461544084559582</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0.6705 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>0.6577 ± 0.0149</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>0.6679 ± 0.0177</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>0.6705 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.0655</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-0.07182387732034179</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-0.08440356452905473</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-0.0655</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.01873795909674028</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.5954974166913147</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.01537663987626775</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.597796051914373</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.01254810544324626</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.01873795909674028</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.5980 ± 0.0187</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0.5955 ± 0.0154</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0.5978 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>0.5980 ± 0.0187</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.01131616346451198</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.6407364849544483</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.0125368861053302</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.6368794588622861</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0.01452284264908751</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0.01131616346451198</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0.6465 ± 0.0113</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>0.6407 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>0.6369 ± 0.0145</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>0.6465 ± 0.0113</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>-0.04849999999999999</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>-0.04523906826313362</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-0.03908340694791312</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-0.04849999999999999</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.0490351347958221</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.4505811915597158</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.04196827183233348</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.5037432322871089</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.04596200128273002</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.0490351347958221</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.4790 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0.4506 ± 0.0420</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0.5037 ± 0.0460</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>0.4790 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.04709328803319829</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.5131743292796098</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.03988950108068751</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.5566850502909479</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0.03148047504906855</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0.04709328803319829</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0.5170 ± 0.0471</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>0.5132 ± 0.0399</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>0.5567 ± 0.0315</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>0.5170 ± 0.0471</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.03800000000000003</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>-0.06259313771989405</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-0.05294181800383901</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>-0.03800000000000003</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.6915000000000001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.01795828499606793</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.6842708000954391</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.01859935929962071</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.6880344473978813</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.02207988225904673</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.6915000000000001</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.01795828499606793</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.6915 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0.6843 ± 0.0186</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0.6880 ± 0.0221</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>0.6915 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.02043961295567453</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.3679534241036536</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.01699372937395863</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.3445775327134274</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.01574036430368459</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0.02043961295567453</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0.3970 ± 0.0204</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>0.3680 ± 0.0170</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>0.3446 ± 0.0157</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>0.3970 ± 0.0204</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.2945000000000001</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.3163173759917855</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.3434569146844539</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0.2945000000000001</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.6824999999999999</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.01889297341459103</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.6620033516331233</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.02172625840012613</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.6586544948108609</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.03419179007442599</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.6824999999999999</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.01889297341459103</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.6825 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0.6620 ± 0.0217</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0.6587 ± 0.0342</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>0.6825 ± 0.0189</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.0196920739836559</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.3668947705602713</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.02080501275150294</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.3387221489716747</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.02024400888026048</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0.0196920739836559</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0.4040 ± 0.0197</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>0.3669 ± 0.0208</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>0.3387 ± 0.0202</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>0.4040 ± 0.0197</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.2784999999999999</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.295108581072852</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.3199323458391862</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0.2784999999999999</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.01901023116347847</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.6603024352232341</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.02103640141418547</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.6582702794717087</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.03322025422810114</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.01901023116347847</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0.6815 ± 0.0190</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0.6603 ± 0.0210</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0.6583 ± 0.0332</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>0.6815 ± 0.0190</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.03825717071492756</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.3598347046068729</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.03555413680180423</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.3324620631174764</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.03334365948789342</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.03825717071492756</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0.3945 ± 0.0383</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>0.3598 ± 0.0356</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>0.3325 ± 0.0333</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>0.3945 ± 0.0383</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.3004677306163611</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.3258082163542322</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>LogReg</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.6565000000000001</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.01375378735718518</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.6313197104590105</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.01421577326312037</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.6373054542536021</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.02103357911065157</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.6565000000000001</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.01375378735718518</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.6565 ± 0.0138</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0.6313 ± 0.0142</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0.6373 ± 0.0210</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>0.6565 ± 0.0138</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.01461544084559584</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.3577613950957352</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.01663777755632596</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.3449775088276731</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.01750160275012201</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0.01461544084559584</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0.4495 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>0.3578 ± 0.0166</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>0.3450 ± 0.0175</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>0.4495 ± 0.0146</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2070000000000001</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2735583153632752</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2923279454259289</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.2070000000000001</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AdaBoost</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.6485000000000001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.0277938842193746</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.6197203841913493</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.02257514059906696</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.6169118549430458</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.02585545016933022</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.6485000000000001</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.0277938842193746</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.6485 ± 0.0278</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0.6197 ± 0.0226</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0.6169 ± 0.0259</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>0.6485 ± 0.0278</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.03786305733972246</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.3965213261129702</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.03866573529246271</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.3775309020878906</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.03355990332230687</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.03786305733972246</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0.4565 ± 0.0379</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>0.3965 ± 0.0387</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>0.3775 ± 0.0336</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>0.4565 ± 0.0379</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.1920000000000001</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0.2231990580783791</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.2393809528551551</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0.1920000000000001</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SVM-RBF</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.01559914527573013</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.6088274369756455</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.01724800626160898</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.5934847271911072</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.01694453727725683</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.01559914527573013</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0.6410 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0.6088 ± 0.0172</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0.5935 ± 0.0169</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>0.6410 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.01358103252497557</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.3566820137587634</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.01683616476888826</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.3471200818130427</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0.01916036594151319</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0.01358103252497557</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0.4520 ± 0.0136</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>0.3567 ± 0.0168</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>0.3471 ± 0.0192</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>0.4520 ± 0.0136</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.1890000000000001</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0.252145423216882</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.2463646453780645</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0.1890000000000001</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.02309401076758502</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.6033478482984258</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.02356654708418312</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.606079712711094</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.02256827610673722</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.02309401076758502</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.6100 ± 0.0231</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0.6033 ± 0.0236</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0.6061 ± 0.0226</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>0.6100 ± 0.0231</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.03169297153067923</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.3582216295942252</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.02919024156897964</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.3581887156779363</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.02728331858398704</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0.03169297153067923</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0.3610 ± 0.0317</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>0.3582 ± 0.0292</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>0.3582 ± 0.0273</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>0.3610 ± 0.0317</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.2489999999999999</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0.2451262187042006</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.2478909970331576</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0.2489999999999999</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.01986062547968833</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.5858781958136642</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.02033358207599369</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.5834680764277166</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.0316096947074111</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.01986062547968833</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.6050 ± 0.0199</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0.5859 ± 0.0203</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0.5835 ± 0.0316</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>0.6050 ± 0.0199</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.02656229575084872</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.3748652676838536</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.02276822334220865</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.353983128703715</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.02023908185962098</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.02656229575084872</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0.4000 ± 0.0266</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>0.3749 ± 0.0228</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>0.3540 ± 0.0202</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>0.4000 ± 0.0266</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0.2110129281298106</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.2294849477240016</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.01873795909674028</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.5954974166913147</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.01537663987626775</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.597796051914373</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.01254810544324626</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.01873795909674028</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.5980 ± 0.0187</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0.5955 ± 0.0154</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0.5978 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>0.5980 ± 0.0187</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0.4595000000000001</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.02842631800911885</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.3577766801027361</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.02948681369571991</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.3435025283610131</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.04901469741189243</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.4595000000000001</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.02842631800911885</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0.4595 ± 0.0284</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>0.3578 ± 0.0295</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>0.3435 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>0.4595 ± 0.0284</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.1384999999999999</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0.2377207365885786</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.2542935235533599</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0.1384999999999999</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.0490351347958221</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.4505811915597158</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.04196827183233348</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.5037432322871089</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.04596200128273002</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.0490351347958221</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.4790 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0.4506 ± 0.0420</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0.5037 ± 0.0460</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>0.4790 ± 0.0490</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.07432847517756719</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.3178181169887249</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.05878019035439856</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.340422379798199</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0.04889451401632575</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0.07432847517756719</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0.3395 ± 0.0743</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>0.3178 ± 0.0588</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>0.3404 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>0.3395 ± 0.0743</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0.1327630745709908</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.1633208524889099</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -7898,31 +12724,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
@@ -8040,6 +12866,44 @@
       </c>
       <c r="E7" t="n">
         <v>0.5376</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.05545000000000001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.0616913272491304</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06503149895936675</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.05545000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2487419442333116</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.266226134133645</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.218</v>
       </c>
     </row>
   </sheetData>
@@ -8057,152 +12921,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -9343,152 +14207,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -10629,152 +15493,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -11915,152 +16779,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -13201,152 +18065,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -14487,152 +19351,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
